--- a/examples/02-styles.xlsx
+++ b/examples/02-styles.xlsx
@@ -16,11 +16,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="#,##0 &quot;UAH&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="d mmmm yyyy"/>
+    <numFmt numFmtId="168" formatCode="0.000E+00"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0,&quot; K&quot;"/>
+    <numFmt numFmtId="170" formatCode="[Green]0.0;[Red]-0.0;[Blue]0"/>
+    <numFmt numFmtId="171" formatCode="000000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,8 +48,27 @@
       <i val="1"/>
       <strike val="1"/>
     </font>
+    <font>
+      <u val="double"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color theme="4" tint="-0.25"/>
+    </font>
+    <font>
+      <outline val="1"/>
+      <shadow val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF7030A0"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -60,8 +85,39 @@
         <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="darkGrid">
+        <fgColor rgb="FF9BC2E6"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear" degree="90">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FF4472C4"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="path" left="0.5" right="0.5" top="0.5" bottom="0.5">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFED7D31"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DFEC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -83,11 +139,28 @@
         <color rgb="FF999999"/>
       </bottom>
     </border>
+    <border>
+      <left style="double"/>
+      <right style="thick">
+        <color rgb="FFC00000"/>
+      </right>
+      <top style="dashDot"/>
+      <bottom style="mediumDashed"/>
+    </border>
+    <border diagonalUp="1" diagonalDown="1">
+      <diagonal style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,6 +177,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -112,11 +192,37 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="13" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment shrinkToFit="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="justify" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment textRotation="255"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Highlight" xfId="1" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -126,6 +232,24 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <i val="1"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -489,14 +613,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -553,6 +678,11 @@
           <t>open</t>
         </is>
       </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Editable</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -574,6 +704,10 @@
           <t>open</t>
         </is>
       </c>
+      <c r="F4" s="9">
+        <f>B3-C3</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -616,30 +750,176 @@
           <t>open</t>
         </is>
       </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Named style</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Wrapped text that does not fit into one line of the cell</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Rotated</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>Italic strike</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Theme color</t>
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Double underline</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Subscript</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Scientific</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>6.02214076e+23</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Theme color + tint</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Fraction</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>1.375</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Outline, shadow</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="n">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>Pattern fill</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Thousands</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="n">
+        <v>1234567.891</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>Gradient fill</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Colored sign</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>-12.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>Path gradient</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Leading zeros</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>Double/thick borders</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>Diagonal border</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>Indented, shrink to fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>Justified, bottom</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>Vertical text</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -656,20 +936,53 @@
         <color rgb="FF638EC6"/>
       </dataBar>
     </cfRule>
+    <cfRule type="top10" rank="1" priority="6" dxfId="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:C6">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
         <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <conditionalFormatting sqref="B3:C6">
+    <cfRule type="iconSet" priority="4">
+      <iconSet iconSet="3Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:A6">
+    <cfRule type="expression" priority="5" dxfId="2">
+      <formula>$D3&lt;0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E6">
+    <cfRule type="duplicateValues" priority="7" dxfId="3"/>
+  </conditionalFormatting>
+  <dataValidations count="5">
     <dataValidation sqref="E3:E6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Choose a status from the list" type="list">
       <formula1>"open,closed,archived"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B3:C6" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Revenue" prompt="Whole number up to 1 000 000" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1000000</formula2>
+    </dataValidation>
+    <dataValidation sqref="D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="date" operator="greaterThan">
+      <formula1>DATE(2026,1,1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="F3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="textLength" errorStyle="warning" operator="lessThanOrEqual">
+      <formula1>20</formula1>
+    </dataValidation>
+    <dataValidation sqref="F5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Multiples of 5 only" type="custom">
+      <formula1>=MOD(F5,5)=0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
